--- a/test/excel/xlsx/saved/arrays-4.xlsx
+++ b/test/excel/xlsx/saved/arrays-4.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11004"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC1BB379-9F48-2B42-8715-E705C08DF747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92986C11-6D64-684C-A721-7D594DF4480F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -216,6 +216,18 @@
     <t>1,5</t>
   </si>
   <si>
+    <t>lift:DB#7</t>
+  </si>
+  <si>
+    <t>lift:DB#8</t>
+  </si>
+  <si>
+    <t>lift:DB#9</t>
+  </si>
+  <si>
+    <t>lift:DB#10</t>
+  </si>
+  <si>
     <t>lift:DCOUNT#1</t>
   </si>
   <si>
@@ -1402,18 +1414,6 @@
   </si>
   <si>
     <t>lift:INTRATE#10</t>
-  </si>
-  <si>
-    <t>lift:IPMT#1</t>
-  </si>
-  <si>
-    <t>lift:IPMT#2</t>
-  </si>
-  <si>
-    <t>lift:IPMT#3</t>
-  </si>
-  <si>
-    <t>lift:IPMT#4</t>
   </si>
   <si>
     <t>end</t>
@@ -3046,20 +3046,20 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="e" cm="1">
-        <f t="array" ref="A1">DCOUNT(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+      <c r="A1" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A1" ca="1">DB(1000000,100000,6,D!B1:B2,7)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B1">
-        <f t="shared" ref="B1:B64" si="0">IF(ISERROR(A1),ERROR.TYPE(A1),IF(ISNUMBER(A1),0,IF(ISLOGICAL(A1),IF(A1,-1,-2),IF(ISTEXT(A1),-3,-4))))</f>
-        <v>3</v>
+        <f t="shared" ref="B1:B64" ca="1" si="0">IF(ISERROR(A1),ERROR.TYPE(A1),IF(ISNUMBER(A1),0,IF(ISLOGICAL(A1),IF(A1,-1,-2),IF(ISTEXT(A1),-3,-4))))</f>
+        <v>9</v>
       </c>
       <c r="C1">
-        <f t="shared" ref="C1:C64" si="1">IF(ISNUMBER(A1),A1,0)</f>
+        <f t="shared" ref="C1:C64" ca="1" si="1">IF(ISNUMBER(A1),A1,0)</f>
         <v>0</v>
       </c>
       <c r="D1" t="str">
-        <f t="shared" ref="D1:D64" si="2">IF(ISTEXT(A1),A1,"")</f>
+        <f t="shared" ref="D1:D64" ca="1" si="2">IF(ISTEXT(A1),A1,"")</f>
         <v/>
       </c>
       <c r="E1" t="s">
@@ -3068,7 +3068,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A2" ca="1">DCOUNT(D!U1:Y7,{1;2},D!AA1:AB2)</f>
+        <f t="array" aca="1" ref="A2" ca="1">DB(1000000,100000,6,{1;2},7)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B2">
@@ -3088,62 +3088,62 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="e" cm="1">
-        <f t="array" ref="A3">DCOUNTA(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+      <c r="A3" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A3" ca="1">DB(1000000,100000,6,1,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B3">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A4" ca="1">DB(1000000,100000,6,1,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="e" cm="1">
+        <f t="array" ref="A5">DCOUNT(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C3">
+      <c r="C5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D5" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="E3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A4" ca="1">DCOUNTA(D!U1:Y7,{1;2},D!AA1:AB2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B4">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D4" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A5" ca="1">DDB(D!B1:B2,300,3650,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B5">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D5" t="str">
-        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="E5" t="s">
@@ -3152,7 +3152,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A6" ca="1">DDB({1;2},300,3650,1)</f>
+        <f t="array" aca="1" ref="A6" ca="1">DCOUNT(D!U1:Y7,{1;2},D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B6">
@@ -3172,20 +3172,20 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A7" ca="1">DDB(2400,D!B1:B2,3650,1)</f>
+      <c r="A7" t="e" cm="1">
+        <f t="array" ref="A7">DCOUNTA(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B7">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C7">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D7" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E7" t="s">
@@ -3194,7 +3194,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A8" ca="1">DDB(2400,{1;2},3650,1)</f>
+        <f t="array" aca="1" ref="A8" ca="1">DCOUNTA(D!U1:Y7,{1;2},D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B8">
@@ -3215,7 +3215,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A9" ca="1">DDB(2400,300,D!B1:B2,1)</f>
+        <f t="array" aca="1" ref="A9" ca="1">DDB(D!B1:B2,300,3650,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B9">
@@ -3236,7 +3236,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A10" ca="1">DDB(2400,300,{1;2},1)</f>
+        <f t="array" aca="1" ref="A10" ca="1">DDB({1;2},300,3650,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B10">
@@ -3257,7 +3257,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A11" ca="1">DDB(2400,300,3650,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A11" ca="1">DDB(2400,D!B1:B2,3650,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B11">
@@ -3278,7 +3278,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A12" ca="1">DDB(2400,300,3650,{1;2})</f>
+        <f t="array" aca="1" ref="A12" ca="1">DDB(2400,{1;2},3650,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B12">
@@ -3298,20 +3298,20 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" t="e" cm="1">
-        <f t="array" ref="A13">DEC2BIN(D!B1:B2,4)</f>
+      <c r="A13" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A13" ca="1">DDB(2400,300,D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B13">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
       </c>
       <c r="C13">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="D13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="E13" t="s">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A14" ca="1">DEC2BIN({1;2},4)</f>
+        <f t="array" aca="1" ref="A14" ca="1">DDB(2400,300,{1;2},1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B14">
@@ -3340,20 +3340,20 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" t="e" cm="1">
-        <f t="array" ref="A15">DEC2BIN(9,D!B1:B2)</f>
+      <c r="A15" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A15" ca="1">DDB(2400,300,3650,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B15">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
       </c>
       <c r="C15">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="D15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="E15" t="s">
@@ -3362,7 +3362,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A16" ca="1">DEC2BIN(9,{1;2})</f>
+        <f t="array" aca="1" ref="A16" ca="1">DDB(2400,300,3650,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B16">
@@ -3383,7 +3383,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="e" cm="1">
-        <f t="array" ref="A17">DEC2HEX(D!B1:B2,4)</f>
+        <f t="array" ref="A17">DEC2BIN(D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B17">
@@ -3404,7 +3404,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A18" ca="1">DEC2HEX({1;2},4)</f>
+        <f t="array" aca="1" ref="A18" ca="1">DEC2BIN({1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B18">
@@ -3425,7 +3425,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="e" cm="1">
-        <f t="array" ref="A19">DEC2HEX(100,D!B1:B2)</f>
+        <f t="array" ref="A19">DEC2BIN(9,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B19">
@@ -3446,7 +3446,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A20" ca="1">DEC2HEX(100,{1;2})</f>
+        <f t="array" aca="1" ref="A20" ca="1">DEC2BIN(9,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B20">
@@ -3467,7 +3467,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="e" cm="1">
-        <f t="array" ref="A21">DEC2OCT(D!B1:B2,3)</f>
+        <f t="array" ref="A21">DEC2HEX(D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B21">
@@ -3488,7 +3488,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A22" ca="1">DEC2OCT({1;2},3)</f>
+        <f t="array" aca="1" ref="A22" ca="1">DEC2HEX({1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B22">
@@ -3509,7 +3509,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="e" cm="1">
-        <f t="array" ref="A23">DEC2OCT(58,D!B1:B2)</f>
+        <f t="array" ref="A23">DEC2HEX(100,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B23">
@@ -3530,7 +3530,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A24" ca="1">DEC2OCT(58,{1;2})</f>
+        <f t="array" aca="1" ref="A24" ca="1">DEC2HEX(100,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B24">
@@ -3550,20 +3550,20 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A25" ca="1">_xlfn.DECIMAL(D!B1:B2,16)</f>
+      <c r="A25" t="e" cm="1">
+        <f t="array" ref="A25">DEC2OCT(D!B1:B2,3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B25">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C25">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E25" t="s">
@@ -3572,7 +3572,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A26" ca="1">_xlfn.DECIMAL({1;2},16)</f>
+        <f t="array" aca="1" ref="A26" ca="1">DEC2OCT({1;2},3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B26">
@@ -3592,20 +3592,20 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A27" ca="1">_xlfn.DECIMAL("FF",D!B1:B2)</f>
+      <c r="A27" t="e" cm="1">
+        <f t="array" ref="A27">DEC2OCT(58,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B27">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C27">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D27" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E27" t="s">
@@ -3614,7 +3614,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A28" ca="1">_xlfn.DECIMAL("FF",{1;2})</f>
+        <f t="array" aca="1" ref="A28" ca="1">DEC2OCT(58,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B28">
@@ -3635,7 +3635,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A29" ca="1">DEGREES(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A29" ca="1">_xlfn.DECIMAL(D!B1:B2,16)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B29">
@@ -3656,7 +3656,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A30" ca="1">DEGREES({1;2})</f>
+        <f t="array" aca="1" ref="A30" ca="1">_xlfn.DECIMAL({1;2},16)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B30">
@@ -3676,20 +3676,20 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="e" cm="1">
-        <f t="array" ref="A31">DELTA(D!B1:B2,4)</f>
+      <c r="A31" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A31" ca="1">_xlfn.DECIMAL("FF",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B31">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
       </c>
       <c r="C31">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="D31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="E31" t="s">
@@ -3698,7 +3698,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A32" ca="1">DELTA({1;2},4)</f>
+        <f t="array" aca="1" ref="A32" ca="1">_xlfn.DECIMAL("FF",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B32">
@@ -3718,20 +3718,20 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="e" cm="1">
-        <f t="array" ref="A33">DELTA(5,D!B1:B2)</f>
+      <c r="A33" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A33" ca="1">DEGREES(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B33">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
       </c>
       <c r="C33">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="D33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="E33" t="s">
@@ -3740,7 +3740,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A34" ca="1">DELTA(5,{1;2})</f>
+        <f t="array" aca="1" ref="A34" ca="1">DEGREES({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B34">
@@ -3761,7 +3761,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="e" cm="1">
-        <f t="array" ref="A35">DGET(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+        <f t="array" ref="A35">DELTA(D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B35">
@@ -3782,7 +3782,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A36" ca="1">DGET(D!U1:Y7,{1;2},D!AA1:AB2)</f>
+        <f t="array" aca="1" ref="A36" ca="1">DELTA({1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B36">
@@ -3803,7 +3803,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="e" cm="1">
-        <f t="array" ref="A37">DISC(D!B1:B2,54058,97.975,100,1)</f>
+        <f t="array" ref="A37">DELTA(5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B37">
@@ -3824,7 +3824,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A38" ca="1">DISC({1;2},54058,97.975,100,1)</f>
+        <f t="array" aca="1" ref="A38" ca="1">DELTA(5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B38">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="e" cm="1">
-        <f t="array" ref="A39">DISC(43282,D!B1:B2,97.975,100,1)</f>
+        <f t="array" ref="A39">DGET(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B39">
@@ -3866,7 +3866,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A40" ca="1">DISC(43282,{1;2},97.975,100,1)</f>
+        <f t="array" aca="1" ref="A40" ca="1">DGET(D!U1:Y7,{1;2},D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B40">
@@ -3887,7 +3887,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="e" cm="1">
-        <f t="array" ref="A41">DISC(43282,54058,D!B1:B2,100,1)</f>
+        <f t="array" ref="A41">DISC(D!B1:B2,54058,97.975,100,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B41">
@@ -3908,7 +3908,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A42" ca="1">DISC(43282,54058,{1;2},100,1)</f>
+        <f t="array" aca="1" ref="A42" ca="1">DISC({1;2},54058,97.975,100,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B42">
@@ -3929,7 +3929,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="e" cm="1">
-        <f t="array" ref="A43">DISC(43282,54058,97.975,D!B1:B2,1)</f>
+        <f t="array" ref="A43">DISC(43282,D!B1:B2,97.975,100,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B43">
@@ -3950,7 +3950,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A44" ca="1">DISC(43282,54058,97.975,{1;2},1)</f>
+        <f t="array" aca="1" ref="A44" ca="1">DISC(43282,{1;2},97.975,100,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B44">
@@ -3971,7 +3971,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="e" cm="1">
-        <f t="array" ref="A45">DISC(43282,54058,97.975,100,D!B1:B2)</f>
+        <f t="array" ref="A45">DISC(43282,54058,D!B1:B2,100,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B45">
@@ -3992,7 +3992,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A46" ca="1">DISC(43282,54058,97.975,100,{1;2})</f>
+        <f t="array" aca="1" ref="A46" ca="1">DISC(43282,54058,{1;2},100,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B46">
@@ -4013,7 +4013,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="e" cm="1">
-        <f t="array" ref="A47">DMAX(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+        <f t="array" ref="A47">DISC(43282,54058,97.975,D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B47">
@@ -4034,7 +4034,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A48" ca="1">DMAX(D!U1:Y7,{1;2},D!AA1:AB2)</f>
+        <f t="array" aca="1" ref="A48" ca="1">DISC(43282,54058,97.975,{1;2},1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B48">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="e" cm="1">
-        <f t="array" ref="A49">DMIN(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+        <f t="array" ref="A49">DISC(43282,54058,97.975,100,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B49">
@@ -4076,7 +4076,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A50" ca="1">DMIN(D!U1:Y7,{1;2},D!AA1:AB2)</f>
+        <f t="array" aca="1" ref="A50" ca="1">DISC(43282,54058,97.975,100,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B50">
@@ -4096,20 +4096,20 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A51" ca="1">DOLLAR(D!B1:B2,2)</f>
+      <c r="A51" t="e" cm="1">
+        <f t="array" ref="A51">DMAX(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B51">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C51">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D51" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E51" t="s">
@@ -4118,7 +4118,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A52" ca="1">DOLLAR({1;2},2)</f>
+        <f t="array" aca="1" ref="A52" ca="1">DMAX(D!U1:Y7,{1;2},D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B52">
@@ -4138,20 +4138,20 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A53" ca="1">DOLLAR(1234.567,D!B1:B2)</f>
+      <c r="A53" t="e" cm="1">
+        <f t="array" ref="A53">DMIN(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B53">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C53">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D53" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E53" t="s">
@@ -4160,7 +4160,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A54" ca="1">DOLLAR(1234.567,{1;2})</f>
+        <f t="array" aca="1" ref="A54" ca="1">DMIN(D!U1:Y7,{1;2},D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B54">
@@ -4180,20 +4180,20 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" t="e" cm="1">
-        <f t="array" ref="A55">DOLLARDE(D!B1:B2,16)</f>
+      <c r="A55" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A55" ca="1">DOLLAR(D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B55">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
       </c>
       <c r="C55">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="D55" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="E55" t="s">
@@ -4202,7 +4202,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A56" ca="1">DOLLARDE({1;2},16)</f>
+        <f t="array" aca="1" ref="A56" ca="1">DOLLAR({1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B56">
@@ -4222,20 +4222,20 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" t="e" cm="1">
-        <f t="array" ref="A57">DOLLARDE(1.02,D!B1:B2)</f>
+      <c r="A57" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A57" ca="1">DOLLAR(1234.567,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B57">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
       </c>
       <c r="C57">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="D57" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="E57" t="s">
@@ -4244,7 +4244,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A58" ca="1">DOLLARDE(1.02,{1;2})</f>
+        <f t="array" aca="1" ref="A58" ca="1">DOLLAR(1234.567,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B58">
@@ -4265,7 +4265,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="e" cm="1">
-        <f t="array" ref="A59">DOLLARFR(D!B1:B2,16)</f>
+        <f t="array" ref="A59">DOLLARDE(D!B1:B2,16)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B59">
@@ -4286,7 +4286,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A60" ca="1">DOLLARFR({1;2},16)</f>
+        <f t="array" aca="1" ref="A60" ca="1">DOLLARDE({1;2},16)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B60">
@@ -4307,7 +4307,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="e" cm="1">
-        <f t="array" ref="A61">DOLLARFR(1.125,D!B1:B2)</f>
+        <f t="array" ref="A61">DOLLARDE(1.02,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B61">
@@ -4328,7 +4328,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A62" ca="1">DOLLARFR(1.125,{1;2})</f>
+        <f t="array" aca="1" ref="A62" ca="1">DOLLARDE(1.02,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B62">
@@ -4349,7 +4349,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="e" cm="1">
-        <f t="array" ref="A63">DPRODUCT(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+        <f t="array" ref="A63">DOLLARFR(D!B1:B2,16)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B63">
@@ -4370,7 +4370,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A64" ca="1">DPRODUCT(D!U1:Y7,{1;2},D!AA1:AB2)</f>
+        <f t="array" aca="1" ref="A64" ca="1">DOLLARFR({1;2},16)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B64">
@@ -4391,7 +4391,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="e" cm="1">
-        <f t="array" ref="A65">DSTDEV(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+        <f t="array" ref="A65">DOLLARFR(1.125,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B65">
@@ -4412,7 +4412,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A66" ca="1">DSTDEV(D!U1:Y7,{1;2},D!AA1:AB2)</f>
+        <f t="array" aca="1" ref="A66" ca="1">DOLLARFR(1.125,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B66">
@@ -4433,7 +4433,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="e" cm="1">
-        <f t="array" ref="A67">DSTDEVP(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+        <f t="array" ref="A67">DPRODUCT(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B67">
@@ -4454,7 +4454,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A68" ca="1">DSTDEVP(D!U1:Y7,{1;2},D!AA1:AB2)</f>
+        <f t="array" aca="1" ref="A68" ca="1">DPRODUCT(D!U1:Y7,{1;2},D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B68">
@@ -4475,7 +4475,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="e" cm="1">
-        <f t="array" ref="A69">DSUM(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+        <f t="array" ref="A69">DSTDEV(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B69">
@@ -4496,7 +4496,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A70" ca="1">DSUM(D!U1:Y7,{1;2},D!AA1:AB2)</f>
+        <f t="array" aca="1" ref="A70" ca="1">DSTDEV(D!U1:Y7,{1;2},D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B70">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="e" cm="1">
-        <f t="array" ref="A71">DURATION(D!B1:B2,DATE(2048,1,1),0.08,0.09,2,1)</f>
+        <f t="array" ref="A71">DSTDEVP(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B71">
@@ -4538,7 +4538,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A72" ca="1">DURATION({1;2},DATE(2048,1,1),0.08,0.09,2,1)</f>
+        <f t="array" aca="1" ref="A72" ca="1">DSTDEVP(D!U1:Y7,{1;2},D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B72">
@@ -4559,7 +4559,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="e" cm="1">
-        <f t="array" ref="A73">DURATION(DATE(2018,7,1),D!B1:B2,0.08,0.09,2,1)</f>
+        <f t="array" ref="A73">DSUM(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B73">
@@ -4580,7 +4580,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A74" ca="1">DURATION(DATE(2018,7,1),{1;2},0.08,0.09,2,1)</f>
+        <f t="array" aca="1" ref="A74" ca="1">DSUM(D!U1:Y7,{1;2},D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B74">
@@ -4601,7 +4601,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="e" cm="1">
-        <f t="array" ref="A75">DURATION(DATE(2018,7,1),DATE(2048,1,1),D!B1:B2,0.09,2,1)</f>
+        <f t="array" ref="A75">DURATION(D!B1:B2,DATE(2048,1,1),0.08,0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B75">
@@ -4622,7 +4622,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A76" ca="1">DURATION(DATE(2018,7,1),DATE(2048,1,1),{1;2},0.09,2,1)</f>
+        <f t="array" aca="1" ref="A76" ca="1">DURATION({1;2},DATE(2048,1,1),0.08,0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B76">
@@ -4643,7 +4643,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="e" cm="1">
-        <f t="array" ref="A77">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,D!B1:B2,2,1)</f>
+        <f t="array" ref="A77">DURATION(DATE(2018,7,1),D!B1:B2,0.08,0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B77">
@@ -4664,7 +4664,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A78" ca="1">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,{1;2},2,1)</f>
+        <f t="array" aca="1" ref="A78" ca="1">DURATION(DATE(2018,7,1),{1;2},0.08,0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B78">
@@ -4685,7 +4685,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="e" cm="1">
-        <f t="array" ref="A79">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,D!B1:B2,1)</f>
+        <f t="array" ref="A79">DURATION(DATE(2018,7,1),DATE(2048,1,1),D!B1:B2,0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B79">
@@ -4706,7 +4706,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A80" ca="1">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,{1;2},1)</f>
+        <f t="array" aca="1" ref="A80" ca="1">DURATION(DATE(2018,7,1),DATE(2048,1,1),{1;2},0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B80">
@@ -4727,7 +4727,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="e" cm="1">
-        <f t="array" ref="A81">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,2,D!B1:B2)</f>
+        <f t="array" ref="A81">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,D!B1:B2,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B81">
@@ -4748,7 +4748,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A82" ca="1">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,2,{1;2})</f>
+        <f t="array" aca="1" ref="A82" ca="1">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,{1;2},2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B82">
@@ -4769,7 +4769,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="e" cm="1">
-        <f t="array" ref="A83">DVAR(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+        <f t="array" ref="A83">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B83">
@@ -4790,7 +4790,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A84" ca="1">DVAR(D!U1:Y7,{1;2},D!AA1:AB2)</f>
+        <f t="array" aca="1" ref="A84" ca="1">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,{1;2},1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B84">
@@ -4811,7 +4811,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="e" cm="1">
-        <f t="array" ref="A85">DVARP(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
+        <f t="array" ref="A85">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B85">
@@ -4832,7 +4832,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A86" ca="1">DVARP(D!U1:Y7,{1;2},D!AA1:AB2)</f>
+        <f t="array" aca="1" ref="A86" ca="1">DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B86">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="e" cm="1">
-        <f t="array" ref="A87">EDATE(D!B1:B2,1)</f>
+        <f t="array" ref="A87">DVAR(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B87">
@@ -4874,7 +4874,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A88" ca="1">EDATE({1;2},1)</f>
+        <f t="array" aca="1" ref="A88" ca="1">DVAR(D!U1:Y7,{1;2},D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B88">
@@ -4895,7 +4895,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="e" cm="1">
-        <f t="array" ref="A89">EDATE(40558,D!B1:B2)</f>
+        <f t="array" ref="A89">DVARP(D!U1:Y7,D!B1:B2,D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B89">
@@ -4916,7 +4916,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A90" ca="1">EDATE(40558,{1;2})</f>
+        <f t="array" aca="1" ref="A90" ca="1">DVARP(D!U1:Y7,{1;2},D!AA1:AB2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B90">
@@ -4937,7 +4937,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="e" cm="1">
-        <f t="array" ref="A91">EFFECT(D!B1:B2,4)</f>
+        <f t="array" ref="A91">EDATE(D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B91">
@@ -4958,7 +4958,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A92" ca="1">EFFECT({1;2},4)</f>
+        <f t="array" aca="1" ref="A92" ca="1">EDATE({1;2},1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B92">
@@ -4979,7 +4979,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="e" cm="1">
-        <f t="array" ref="A93">EFFECT(0.0525,D!B1:B2)</f>
+        <f t="array" ref="A93">EDATE(40558,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B93">
@@ -5000,7 +5000,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A94" ca="1">EFFECT(0.0525,{1;2})</f>
+        <f t="array" aca="1" ref="A94" ca="1">EDATE(40558,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B94">
@@ -5021,7 +5021,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="e" cm="1">
-        <f t="array" ref="A95">EOMONTH(D!B1:B2,1)</f>
+        <f t="array" ref="A95">EFFECT(D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B95">
@@ -5042,7 +5042,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A96" ca="1">EOMONTH({1;2},1)</f>
+        <f t="array" aca="1" ref="A96" ca="1">EFFECT({1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B96">
@@ -5063,7 +5063,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="e" cm="1">
-        <f t="array" ref="A97">EOMONTH(40544,D!B1:B2)</f>
+        <f t="array" ref="A97">EFFECT(0.0525,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B97">
@@ -5084,7 +5084,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A98" ca="1">EOMONTH(40544,{1;2})</f>
+        <f t="array" aca="1" ref="A98" ca="1">EFFECT(0.0525,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B98">
@@ -5105,7 +5105,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="e" cm="1">
-        <f t="array" ref="A99">ERF(D!B1:B2)</f>
+        <f t="array" ref="A99">EOMONTH(D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B99">
@@ -5126,7 +5126,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A100" ca="1">ERF({1;2})</f>
+        <f t="array" aca="1" ref="A100" ca="1">EOMONTH({1;2},1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B100">
@@ -5147,7 +5147,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="e" cm="1">
-        <f t="array" ref="A101">_xlfn.ERF.PRECISE(D!B1:B2)</f>
+        <f t="array" ref="A101">EOMONTH(40544,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B101">
@@ -5168,7 +5168,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A102" ca="1">_xlfn.ERF.PRECISE({1;2})</f>
+        <f t="array" aca="1" ref="A102" ca="1">EOMONTH(40544,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B102">
@@ -5189,7 +5189,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="e" cm="1">
-        <f t="array" ref="A103">ERFC(D!B1:B2)</f>
+        <f t="array" ref="A103">ERF(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B103">
@@ -5210,7 +5210,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A104" ca="1">ERFC({1;2})</f>
+        <f t="array" aca="1" ref="A104" ca="1">ERF({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B104">
@@ -5231,7 +5231,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="e" cm="1">
-        <f t="array" ref="A105">_xlfn.ERFC.PRECISE(D!B1:B2)</f>
+        <f t="array" ref="A105">_xlfn.ERF.PRECISE(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B105">
@@ -5252,7 +5252,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A106" ca="1">_xlfn.ERFC.PRECISE({1;2})</f>
+        <f t="array" aca="1" ref="A106" ca="1">_xlfn.ERF.PRECISE({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B106">
@@ -5272,20 +5272,20 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A107" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A107" ca="1">ERROR.TYPE(D!B1:B2)</f>
+      <c r="A107" t="e" cm="1">
+        <f t="array" ref="A107">ERFC(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B107">
-        <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="C107">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D107" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E107" t="s">
@@ -5294,7 +5294,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A108" ca="1">ERROR.TYPE({1;2})</f>
+        <f t="array" aca="1" ref="A108" ca="1">ERFC({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B108">
@@ -5314,20 +5314,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A109" ca="1">EVEN(D!B1:B2)</f>
+      <c r="A109" t="e" cm="1">
+        <f t="array" ref="A109">_xlfn.ERFC.PRECISE(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B109">
-        <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="C109">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D109" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E109" t="s">
@@ -5336,7 +5336,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A110" ca="1">EVEN({1;2})</f>
+        <f t="array" aca="1" ref="A110" ca="1">_xlfn.ERFC.PRECISE({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B110">
@@ -5357,7 +5357,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A111" ca="1">EXACT(D!B1:B2,"word")</f>
+        <f t="array" aca="1" ref="A111" ca="1">ERROR.TYPE(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B111">
@@ -5378,7 +5378,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A112" ca="1">EXACT({1;2},"word")</f>
+        <f t="array" aca="1" ref="A112" ca="1">ERROR.TYPE({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B112">
@@ -5399,7 +5399,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A113" ca="1">EXACT("word",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A113" ca="1">EVEN(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B113">
@@ -5420,7 +5420,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A114" ca="1">EXACT("word",{1;2})</f>
+        <f t="array" aca="1" ref="A114" ca="1">EVEN({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B114">
@@ -5441,7 +5441,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A115" ca="1">EXP(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A115" ca="1">EXACT(D!B1:B2,"word")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B115">
@@ -5462,7 +5462,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A116" ca="1">EXP({1;2})</f>
+        <f t="array" aca="1" ref="A116" ca="1">EXACT({1;2},"word")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B116">
@@ -5483,7 +5483,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A117" ca="1">_xlfn.EXPON.DIST(D!B1:B2,10,TRUE)</f>
+        <f t="array" aca="1" ref="A117" ca="1">EXACT("word",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B117">
@@ -5504,7 +5504,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A118" ca="1">_xlfn.EXPON.DIST({1;2},10,TRUE)</f>
+        <f t="array" aca="1" ref="A118" ca="1">EXACT("word",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B118">
@@ -5525,7 +5525,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A119" ca="1">_xlfn.EXPON.DIST(0.2,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A119" ca="1">EXP(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B119">
@@ -5546,7 +5546,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A120" ca="1">_xlfn.EXPON.DIST(0.2,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A120" ca="1">EXP({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B120">
@@ -5567,7 +5567,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A121" ca="1">_xlfn.EXPON.DIST(0.2,10,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A121" ca="1">_xlfn.EXPON.DIST(D!B1:B2,10,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B121">
@@ -5588,7 +5588,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A122" ca="1">_xlfn.EXPON.DIST(0.2,10,{1;2})</f>
+        <f t="array" aca="1" ref="A122" ca="1">_xlfn.EXPON.DIST({1;2},10,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B122">
@@ -5609,7 +5609,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A123" ca="1">EXPONDIST(D!B1:B2,10,TRUE)</f>
+        <f t="array" aca="1" ref="A123" ca="1">_xlfn.EXPON.DIST(0.2,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B123">
@@ -5630,7 +5630,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A124" ca="1">EXPONDIST({1;2},10,TRUE)</f>
+        <f t="array" aca="1" ref="A124" ca="1">_xlfn.EXPON.DIST(0.2,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B124">
@@ -5651,7 +5651,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A125" ca="1">EXPONDIST(0.2,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A125" ca="1">_xlfn.EXPON.DIST(0.2,10,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B125">
@@ -5672,7 +5672,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A126" ca="1">EXPONDIST(0.2,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A126" ca="1">_xlfn.EXPON.DIST(0.2,10,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B126">
@@ -5693,7 +5693,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A127" ca="1">EXPONDIST(0.2,10,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A127" ca="1">EXPONDIST(D!B1:B2,10,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B127">
@@ -5714,7 +5714,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A128" ca="1">EXPONDIST(0.2,10,{1;2})</f>
+        <f t="array" aca="1" ref="A128" ca="1">EXPONDIST({1;2},10,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B128">
@@ -5735,7 +5735,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A129" ca="1">_xlfn.F.DIST(D!B1:B2,6,4,TRUE)</f>
+        <f t="array" aca="1" ref="A129" ca="1">EXPONDIST(0.2,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B129">
@@ -5756,7 +5756,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A130" ca="1">_xlfn.F.DIST({1;2},6,4,TRUE)</f>
+        <f t="array" aca="1" ref="A130" ca="1">EXPONDIST(0.2,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B130">
@@ -5777,7 +5777,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A131" ca="1">_xlfn.F.DIST(15.2069,D!B1:B2,4,TRUE)</f>
+        <f t="array" aca="1" ref="A131" ca="1">EXPONDIST(0.2,10,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B131">
@@ -5798,7 +5798,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A132" ca="1">_xlfn.F.DIST(15.2069,{1;2},4,TRUE)</f>
+        <f t="array" aca="1" ref="A132" ca="1">EXPONDIST(0.2,10,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B132">
@@ -5819,7 +5819,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A133" ca="1">_xlfn.F.DIST(15.2069,6,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A133" ca="1">_xlfn.F.DIST(D!B1:B2,6,4,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B133">
@@ -5840,7 +5840,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A134" ca="1">_xlfn.F.DIST(15.2069,6,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A134" ca="1">_xlfn.F.DIST({1;2},6,4,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B134">
@@ -5861,7 +5861,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A135" ca="1">_xlfn.F.DIST(15.2069,6,4,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A135" ca="1">_xlfn.F.DIST(15.2069,D!B1:B2,4,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B135">
@@ -5882,7 +5882,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A136" ca="1">_xlfn.F.DIST(15.2069,6,4,{1;2})</f>
+        <f t="array" aca="1" ref="A136" ca="1">_xlfn.F.DIST(15.2069,{1;2},4,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B136">
@@ -5903,7 +5903,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A137" ca="1">_xlfn.F.DIST.RT(D!B1:B2,6,4)</f>
+        <f t="array" aca="1" ref="A137" ca="1">_xlfn.F.DIST(15.2069,6,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B137">
@@ -5924,7 +5924,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A138" ca="1">_xlfn.F.DIST.RT({1;2},6,4)</f>
+        <f t="array" aca="1" ref="A138" ca="1">_xlfn.F.DIST(15.2069,6,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B138">
@@ -5945,7 +5945,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A139" ca="1">_xlfn.F.DIST.RT(15.2069,D!B1:B2,4)</f>
+        <f t="array" aca="1" ref="A139" ca="1">_xlfn.F.DIST(15.2069,6,4,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B139">
@@ -5966,7 +5966,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A140" ca="1">_xlfn.F.DIST.RT(15.2069,{1;2},4)</f>
+        <f t="array" aca="1" ref="A140" ca="1">_xlfn.F.DIST(15.2069,6,4,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B140">
@@ -5987,7 +5987,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A141" ca="1">_xlfn.F.DIST.RT(15.2069,6,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A141" ca="1">_xlfn.F.DIST.RT(D!B1:B2,6,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B141">
@@ -6008,7 +6008,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A142" ca="1">_xlfn.F.DIST.RT(15.2069,6,{1;2})</f>
+        <f t="array" aca="1" ref="A142" ca="1">_xlfn.F.DIST.RT({1;2},6,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B142">
@@ -6029,7 +6029,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A143" ca="1">_xlfn.F.INV(D!B1:B2,6,4)</f>
+        <f t="array" aca="1" ref="A143" ca="1">_xlfn.F.DIST.RT(15.2069,D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B143">
@@ -6050,7 +6050,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A144" ca="1">_xlfn.F.INV({1;2},6,4)</f>
+        <f t="array" aca="1" ref="A144" ca="1">_xlfn.F.DIST.RT(15.2069,{1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B144">
@@ -6071,7 +6071,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A145" ca="1">_xlfn.F.INV(0.01,D!B1:B2,4)</f>
+        <f t="array" aca="1" ref="A145" ca="1">_xlfn.F.DIST.RT(15.2069,6,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B145">
@@ -6092,7 +6092,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A146" ca="1">_xlfn.F.INV(0.01,{1;2},4)</f>
+        <f t="array" aca="1" ref="A146" ca="1">_xlfn.F.DIST.RT(15.2069,6,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B146">
@@ -6113,7 +6113,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A147" ca="1">_xlfn.F.INV(0.01,6,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A147" ca="1">_xlfn.F.INV(D!B1:B2,6,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B147">
@@ -6134,7 +6134,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A148" ca="1">_xlfn.F.INV(0.01,6,{1;2})</f>
+        <f t="array" aca="1" ref="A148" ca="1">_xlfn.F.INV({1;2},6,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B148">
@@ -6155,7 +6155,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A149" ca="1">_xlfn.F.INV.RT(D!B1:B2,6,4)</f>
+        <f t="array" aca="1" ref="A149" ca="1">_xlfn.F.INV(0.01,D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B149">
@@ -6176,7 +6176,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A150" ca="1">_xlfn.F.INV.RT({1;2},6,4)</f>
+        <f t="array" aca="1" ref="A150" ca="1">_xlfn.F.INV(0.01,{1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B150">
@@ -6197,7 +6197,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A151" ca="1">_xlfn.F.INV.RT(0.01,D!B1:B2,4)</f>
+        <f t="array" aca="1" ref="A151" ca="1">_xlfn.F.INV(0.01,6,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B151">
@@ -6218,7 +6218,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A152" ca="1">_xlfn.F.INV.RT(0.01,{1;2},4)</f>
+        <f t="array" aca="1" ref="A152" ca="1">_xlfn.F.INV(0.01,6,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B152">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A153" ca="1">_xlfn.F.INV.RT(0.01,6,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A153" ca="1">_xlfn.F.INV.RT(D!B1:B2,6,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B153">
@@ -6260,7 +6260,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A154" ca="1">_xlfn.F.INV.RT(0.01,6,{1;2})</f>
+        <f t="array" aca="1" ref="A154" ca="1">_xlfn.F.INV.RT({1;2},6,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B154">
@@ -6281,7 +6281,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A155" ca="1">FACT(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A155" ca="1">_xlfn.F.INV.RT(0.01,D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B155">
@@ -6302,7 +6302,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A156" ca="1">FACT({1;2})</f>
+        <f t="array" aca="1" ref="A156" ca="1">_xlfn.F.INV.RT(0.01,{1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B156">
@@ -6322,104 +6322,104 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A157" t="e" cm="1">
-        <f t="array" ref="A157">FACTDOUBLE(D!B1:B2)</f>
+      <c r="A157" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A157" ca="1">_xlfn.F.INV.RT(0.01,6,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B157">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C157">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D157" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E157" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A158" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A158" ca="1">_xlfn.F.INV.RT(0.01,6,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B158">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C158">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D158" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E158" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A159" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A159" ca="1">FACT(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B159">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C159">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D159" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E159" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A160" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A160" ca="1">FACT({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B160">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C160">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D160" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E160" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A161" t="e" cm="1">
+        <f t="array" ref="A161">FACTDOUBLE(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B161">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="C157">
+      <c r="C161">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="D157" t="str">
+      <c r="D161" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="E157" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A158" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A158" ca="1">FACTDOUBLE({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B158">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C158">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D158" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E158" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A159" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A159" ca="1">FDIST(D!B1:B2,6,4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B159">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C159">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D159" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E159" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A160" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A160" ca="1">FDIST({1;2},6,4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B160">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C160">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D160" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E160" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A161" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A161" ca="1">FDIST(15.2069,D!B1:B2,4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B161">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C161">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D161" t="str">
-        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E161" t="s">
@@ -6428,7 +6428,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A162" ca="1">FDIST(15.2069,{1;2},4)</f>
+        <f t="array" aca="1" ref="A162" ca="1">FACTDOUBLE({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B162">
@@ -6449,7 +6449,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A163" ca="1">FDIST(15.2069,6,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A163" ca="1">FDIST(D!B1:B2,6,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B163">
@@ -6470,7 +6470,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A164" ca="1">FDIST(15.2069,6,{1;2})</f>
+        <f t="array" aca="1" ref="A164" ca="1">FDIST({1;2},6,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B164">
@@ -6491,7 +6491,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A165" ca="1">FIND(D!B1:B2,"Miriam McGovern")</f>
+        <f t="array" aca="1" ref="A165" ca="1">FDIST(15.2069,D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B165">
@@ -6512,7 +6512,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A166" ca="1">FIND({1;2},"Miriam McGovern")</f>
+        <f t="array" aca="1" ref="A166" ca="1">FDIST(15.2069,{1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B166">
@@ -6533,7 +6533,7 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A167" ca="1">FIND("M",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A167" ca="1">FDIST(15.2069,6,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B167">
@@ -6554,7 +6554,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A168" ca="1">FIND("M",{1;2})</f>
+        <f t="array" aca="1" ref="A168" ca="1">FDIST(15.2069,6,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B168">
@@ -6575,7 +6575,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A169" ca="1">FINDB(D!B1:B2,"abc")</f>
+        <f t="array" aca="1" ref="A169" ca="1">FIND(D!B1:B2,"Miriam McGovern")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B169">
@@ -6596,7 +6596,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A170" ca="1">FINDB({1;2},"abc")</f>
+        <f t="array" aca="1" ref="A170" ca="1">FIND({1;2},"Miriam McGovern")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B170">
@@ -6617,7 +6617,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A171" ca="1">FINDB("b",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A171" ca="1">FIND("M",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B171">
@@ -6638,7 +6638,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A172" ca="1">FINDB("b",{1;2})</f>
+        <f t="array" aca="1" ref="A172" ca="1">FIND("M",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B172">
@@ -6659,7 +6659,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A173" ca="1">FINV(D!B1:B2,6,4)</f>
+        <f t="array" aca="1" ref="A173" ca="1">FINDB(D!B1:B2,"abc")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B173">
@@ -6680,7 +6680,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A174" ca="1">FINV({1;2},6,4)</f>
+        <f t="array" aca="1" ref="A174" ca="1">FINDB({1;2},"abc")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B174">
@@ -6701,7 +6701,7 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A175" ca="1">FINV(0.01,D!B1:B2,4)</f>
+        <f t="array" aca="1" ref="A175" ca="1">FINDB("b",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B175">
@@ -6722,7 +6722,7 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A176" ca="1">FINV(0.01,{1;2},4)</f>
+        <f t="array" aca="1" ref="A176" ca="1">FINDB("b",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B176">
@@ -6743,7 +6743,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A177" ca="1">FINV(0.01,6,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A177" ca="1">FINV(D!B1:B2,6,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B177">
@@ -6764,7 +6764,7 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A178" ca="1">FINV(0.01,6,{1;2})</f>
+        <f t="array" aca="1" ref="A178" ca="1">FINV({1;2},6,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B178">
@@ -6785,7 +6785,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A179" ca="1">FISHER(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A179" ca="1">FINV(0.01,D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B179">
@@ -6806,7 +6806,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A180" ca="1">FISHER({1;2})</f>
+        <f t="array" aca="1" ref="A180" ca="1">FINV(0.01,{1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B180">
@@ -6827,7 +6827,7 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A181" ca="1">FISHERINV(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A181" ca="1">FINV(0.01,6,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B181">
@@ -6848,7 +6848,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A182" ca="1">FISHERINV({1;2})</f>
+        <f t="array" aca="1" ref="A182" ca="1">FINV(0.01,6,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B182">
@@ -6869,7 +6869,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A183" ca="1">FIXED(D!B1:B2,1)</f>
+        <f t="array" aca="1" ref="A183" ca="1">FISHER(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B183">
@@ -6890,7 +6890,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A184" ca="1">FIXED({1;2},1)</f>
+        <f t="array" aca="1" ref="A184" ca="1">FISHER({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B184">
@@ -6911,7 +6911,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A185" ca="1">FIXED(1234.567,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A185" ca="1">FISHERINV(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B185">
@@ -6932,7 +6932,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A186" ca="1">FIXED(1234.567,{1;2})</f>
+        <f t="array" aca="1" ref="A186" ca="1">FISHERINV({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B186">
@@ -6953,7 +6953,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A187" ca="1">FLOOR(D!B1:B2,2)</f>
+        <f t="array" aca="1" ref="A187" ca="1">FIXED(D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B187">
@@ -6974,7 +6974,7 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A188" ca="1">FLOOR({1;2},2)</f>
+        <f t="array" aca="1" ref="A188" ca="1">FIXED({1;2},1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B188">
@@ -6995,7 +6995,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A189" ca="1">FLOOR(3.7,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A189" ca="1">FIXED(1234.567,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B189">
@@ -7016,7 +7016,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A190" ca="1">FLOOR(3.7,{1;2})</f>
+        <f t="array" aca="1" ref="A190" ca="1">FIXED(1234.567,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B190">
@@ -7037,7 +7037,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A191" ca="1">_xlfn.FLOOR.MATH(D!B1:B2,5)</f>
+        <f t="array" aca="1" ref="A191" ca="1">FLOOR(D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B191">
@@ -7058,7 +7058,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A192" ca="1">_xlfn.FLOOR.MATH({1;2},5)</f>
+        <f t="array" aca="1" ref="A192" ca="1">FLOOR({1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B192">
@@ -7079,7 +7079,7 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A193" ca="1">_xlfn.FLOOR.MATH(24.3,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A193" ca="1">FLOOR(3.7,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B193">
@@ -7100,7 +7100,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A194" ca="1">_xlfn.FLOOR.MATH(24.3,{1;2})</f>
+        <f t="array" aca="1" ref="A194" ca="1">FLOOR(3.7,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B194">
@@ -7121,7 +7121,7 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A195" ca="1">_xlfn.FLOOR.PRECISE(D!B1:B2,-1)</f>
+        <f t="array" aca="1" ref="A195" ca="1">_xlfn.FLOOR.MATH(D!B1:B2,5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B195">
@@ -7142,7 +7142,7 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A196" ca="1">_xlfn.FLOOR.PRECISE({1;2},-1)</f>
+        <f t="array" aca="1" ref="A196" ca="1">_xlfn.FLOOR.MATH({1;2},5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B196">
@@ -7163,7 +7163,7 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A197" ca="1">_xlfn.FLOOR.PRECISE(-3.2,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A197" ca="1">_xlfn.FLOOR.MATH(24.3,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B197">
@@ -7184,7 +7184,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A198" ca="1">_xlfn.FLOOR.PRECISE(-3.2,{1;2})</f>
+        <f t="array" aca="1" ref="A198" ca="1">_xlfn.FLOOR.MATH(24.3,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B198">
@@ -7205,7 +7205,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A199" ca="1">FORECAST(D!B1:B2,D!C1:C8,D!B1:B8)</f>
+        <f t="array" aca="1" ref="A199" ca="1">_xlfn.FLOOR.PRECISE(D!B1:B2,-1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B199">
@@ -7226,7 +7226,7 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A200" ca="1">FORECAST({1;2},D!C1:C8,D!B1:B8)</f>
+        <f t="array" aca="1" ref="A200" ca="1">_xlfn.FLOOR.PRECISE({1;2},-1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B200">
@@ -7247,7 +7247,7 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A201" ca="1">_xlfn.FORECAST.LINEAR(D!B1:B2,D!AY1:AY5,D!AZ1:AZ5)</f>
+        <f t="array" aca="1" ref="A201" ca="1">_xlfn.FLOOR.PRECISE(-3.2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B201">
@@ -7268,7 +7268,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A202" ca="1">_xlfn.FORECAST.LINEAR({1;2},D!AY1:AY5,D!AZ1:AZ5)</f>
+        <f t="array" aca="1" ref="A202" ca="1">_xlfn.FLOOR.PRECISE(-3.2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B202">
@@ -7289,7 +7289,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A203" ca="1">FV(D!B1:B2,10,-200,-500,1)</f>
+        <f t="array" aca="1" ref="A203" ca="1">FORECAST(D!B1:B2,D!C1:C8,D!B1:B8)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B203">
@@ -7310,7 +7310,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A204" ca="1">FV({1;2},10,-200,-500,1)</f>
+        <f t="array" aca="1" ref="A204" ca="1">FORECAST({1;2},D!C1:C8,D!B1:B8)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B204">
@@ -7331,7 +7331,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A205" ca="1">FV(0.005,D!B1:B2,-200,-500,1)</f>
+        <f t="array" aca="1" ref="A205" ca="1">_xlfn.FORECAST.LINEAR(D!B1:B2,D!AY1:AY5,D!AZ1:AZ5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B205">
@@ -7352,7 +7352,7 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A206" ca="1">FV(0.005,{1;2},-200,-500,1)</f>
+        <f t="array" aca="1" ref="A206" ca="1">_xlfn.FORECAST.LINEAR({1;2},D!AY1:AY5,D!AZ1:AZ5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B206">
@@ -7373,7 +7373,7 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A207" ca="1">FV(0.005,10,D!B1:B2,-500,1)</f>
+        <f t="array" aca="1" ref="A207" ca="1">FV(D!B1:B2,10,-200,-500,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B207">
@@ -7394,7 +7394,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A208" ca="1">FV(0.005,10,{1;2},-500,1)</f>
+        <f t="array" aca="1" ref="A208" ca="1">FV({1;2},10,-200,-500,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B208">
@@ -7415,7 +7415,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A209" ca="1">FV(0.005,10,-200,D!B1:B2,1)</f>
+        <f t="array" aca="1" ref="A209" ca="1">FV(0.005,D!B1:B2,-200,-500,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B209">
@@ -7436,7 +7436,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A210" ca="1">FV(0.005,10,-200,{1;2},1)</f>
+        <f t="array" aca="1" ref="A210" ca="1">FV(0.005,{1;2},-200,-500,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B210">
@@ -7457,7 +7457,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A211" ca="1">FV(0.005,10,-200,-500,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A211" ca="1">FV(0.005,10,D!B1:B2,-500,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B211">
@@ -7478,7 +7478,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A212" ca="1">FV(0.005,10,-200,-500,{1;2})</f>
+        <f t="array" aca="1" ref="A212" ca="1">FV(0.005,10,{1;2},-500,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B212">
@@ -7498,104 +7498,104 @@
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A213" t="e" cm="1">
-        <f t="array" ref="A213">FVSCHEDULE(D!B1:B2,D!AQ1:AQ3)</f>
+      <c r="A213" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A213" ca="1">FV(0.005,10,-200,D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B213">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C213">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D213" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E213" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A214" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A214" ca="1">FV(0.005,10,-200,{1;2},1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B214">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C214">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D214" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E214" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A215" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A215" ca="1">FV(0.005,10,-200,-500,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B215">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C215">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D215" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E215" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A216" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A216" ca="1">FV(0.005,10,-200,-500,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B216">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C216">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D216" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E216" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A217" t="e" cm="1">
+        <f t="array" ref="A217">FVSCHEDULE(D!B1:B2,D!AQ1:AQ3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B217">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C213">
+      <c r="C217">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="D213" t="str">
+      <c r="D217" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="E213" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A214" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A214" ca="1">FVSCHEDULE({1;2},D!AQ1:AQ3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B214">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C214">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D214" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E214" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A215" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A215" ca="1">_xlfn.GAMMA(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B215">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C215">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D215" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E215" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A216" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A216" ca="1">_xlfn.GAMMA({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B216">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C216">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D216" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E216" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A217" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A217" ca="1">_xlfn.GAMMA.DIST(D!B1:B2,9,2,FALSE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B217">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C217">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D217" t="str">
-        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="E217" t="s">
@@ -7604,7 +7604,7 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A218" ca="1">_xlfn.GAMMA.DIST({1;2},9,2,FALSE)</f>
+        <f t="array" aca="1" ref="A218" ca="1">FVSCHEDULE({1;2},D!AQ1:AQ3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B218">
@@ -7625,7 +7625,7 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A219" ca="1">_xlfn.GAMMA.DIST(10.00001131,D!B1:B2,2,FALSE)</f>
+        <f t="array" aca="1" ref="A219" ca="1">_xlfn.GAMMA(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B219">
@@ -7646,7 +7646,7 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A220" ca="1">_xlfn.GAMMA.DIST(10.00001131,{1;2},2,FALSE)</f>
+        <f t="array" aca="1" ref="A220" ca="1">_xlfn.GAMMA({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B220">
@@ -7667,7 +7667,7 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A221" ca="1">_xlfn.GAMMA.DIST(10.00001131,9,D!B1:B2,FALSE)</f>
+        <f t="array" aca="1" ref="A221" ca="1">_xlfn.GAMMA.DIST(D!B1:B2,9,2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B221">
@@ -7688,7 +7688,7 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A222" ca="1">_xlfn.GAMMA.DIST(10.00001131,9,{1;2},FALSE)</f>
+        <f t="array" aca="1" ref="A222" ca="1">_xlfn.GAMMA.DIST({1;2},9,2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B222">
@@ -7709,7 +7709,7 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A223" ca="1">_xlfn.GAMMA.DIST(10.00001131,9,2,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A223" ca="1">_xlfn.GAMMA.DIST(10.00001131,D!B1:B2,2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B223">
@@ -7730,7 +7730,7 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A224" ca="1">_xlfn.GAMMA.DIST(10.00001131,9,2,{1;2})</f>
+        <f t="array" aca="1" ref="A224" ca="1">_xlfn.GAMMA.DIST(10.00001131,{1;2},2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B224">
@@ -7751,7 +7751,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A225" ca="1">_xlfn.GAMMA.INV(D!B1:B2,9,2)</f>
+        <f t="array" aca="1" ref="A225" ca="1">_xlfn.GAMMA.DIST(10.00001131,9,D!B1:B2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B225">
@@ -7772,7 +7772,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A226" ca="1">_xlfn.GAMMA.INV({1;2},9,2)</f>
+        <f t="array" aca="1" ref="A226" ca="1">_xlfn.GAMMA.DIST(10.00001131,9,{1;2},FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B226">
@@ -7793,7 +7793,7 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A227" ca="1">_xlfn.GAMMA.INV(0.068094,D!B1:B2,2)</f>
+        <f t="array" aca="1" ref="A227" ca="1">_xlfn.GAMMA.DIST(10.00001131,9,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B227">
@@ -7814,7 +7814,7 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A228" ca="1">_xlfn.GAMMA.INV(0.068094,{1;2},2)</f>
+        <f t="array" aca="1" ref="A228" ca="1">_xlfn.GAMMA.DIST(10.00001131,9,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B228">
@@ -7835,7 +7835,7 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A229" ca="1">_xlfn.GAMMA.INV(0.068094,9,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A229" ca="1">_xlfn.GAMMA.INV(D!B1:B2,9,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B229">
@@ -7856,7 +7856,7 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A230" ca="1">_xlfn.GAMMA.INV(0.068094,9,{1;2})</f>
+        <f t="array" aca="1" ref="A230" ca="1">_xlfn.GAMMA.INV({1;2},9,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B230">
@@ -7877,7 +7877,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A231" ca="1">GAMMADIST(D!B1:B2,9,2,FALSE)</f>
+        <f t="array" aca="1" ref="A231" ca="1">_xlfn.GAMMA.INV(0.068094,D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B231">
@@ -7898,7 +7898,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A232" ca="1">GAMMADIST({1;2},9,2,FALSE)</f>
+        <f t="array" aca="1" ref="A232" ca="1">_xlfn.GAMMA.INV(0.068094,{1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B232">
@@ -7919,7 +7919,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A233" ca="1">GAMMADIST(10.00001131,D!B1:B2,2,FALSE)</f>
+        <f t="array" aca="1" ref="A233" ca="1">_xlfn.GAMMA.INV(0.068094,9,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B233">
@@ -7940,7 +7940,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A234" ca="1">GAMMADIST(10.00001131,{1;2},2,FALSE)</f>
+        <f t="array" aca="1" ref="A234" ca="1">_xlfn.GAMMA.INV(0.068094,9,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B234">
@@ -7961,7 +7961,7 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A235" ca="1">GAMMADIST(10.00001131,9,D!B1:B2,FALSE)</f>
+        <f t="array" aca="1" ref="A235" ca="1">GAMMADIST(D!B1:B2,9,2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B235">
@@ -7982,7 +7982,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A236" ca="1">GAMMADIST(10.00001131,9,{1;2},FALSE)</f>
+        <f t="array" aca="1" ref="A236" ca="1">GAMMADIST({1;2},9,2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B236">
@@ -8003,7 +8003,7 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A237" ca="1">GAMMADIST(10.00001131,9,2,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A237" ca="1">GAMMADIST(10.00001131,D!B1:B2,2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B237">
@@ -8024,7 +8024,7 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A238" ca="1">GAMMADIST(10.00001131,9,2,{1;2})</f>
+        <f t="array" aca="1" ref="A238" ca="1">GAMMADIST(10.00001131,{1;2},2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B238">
@@ -8045,7 +8045,7 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A239" ca="1">GAMMAINV(D!B1:B2,9,2)</f>
+        <f t="array" aca="1" ref="A239" ca="1">GAMMADIST(10.00001131,9,D!B1:B2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B239">
@@ -8066,7 +8066,7 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A240" ca="1">GAMMAINV({1;2},9,2)</f>
+        <f t="array" aca="1" ref="A240" ca="1">GAMMADIST(10.00001131,9,{1;2},FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B240">
@@ -8087,7 +8087,7 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A241" ca="1">GAMMAINV(0.068094,D!B1:B2,2)</f>
+        <f t="array" aca="1" ref="A241" ca="1">GAMMADIST(10.00001131,9,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B241">
@@ -8108,7 +8108,7 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A242" ca="1">GAMMAINV(0.068094,{1;2},2)</f>
+        <f t="array" aca="1" ref="A242" ca="1">GAMMADIST(10.00001131,9,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B242">
@@ -8129,7 +8129,7 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A243" ca="1">GAMMAINV(0.068094,9,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A243" ca="1">GAMMAINV(D!B1:B2,9,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B243">
@@ -8150,7 +8150,7 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A244" ca="1">GAMMAINV(0.068094,9,{1;2})</f>
+        <f t="array" aca="1" ref="A244" ca="1">GAMMAINV({1;2},9,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B244">
@@ -8171,7 +8171,7 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A245" ca="1">GAMMALN(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A245" ca="1">GAMMAINV(0.068094,D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B245">
@@ -8192,7 +8192,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A246" ca="1">GAMMALN({1;2})</f>
+        <f t="array" aca="1" ref="A246" ca="1">GAMMAINV(0.068094,{1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B246">
@@ -8213,7 +8213,7 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A247" ca="1">_xlfn.GAMMALN.PRECISE(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A247" ca="1">GAMMAINV(0.068094,9,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B247">
@@ -8234,7 +8234,7 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A248" ca="1">_xlfn.GAMMALN.PRECISE({1;2})</f>
+        <f t="array" aca="1" ref="A248" ca="1">GAMMAINV(0.068094,9,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B248">
@@ -8255,7 +8255,7 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A249" ca="1">_xlfn.GAUSS(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A249" ca="1">GAMMALN(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B249">
@@ -8276,7 +8276,7 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A250" ca="1">_xlfn.GAUSS({1;2})</f>
+        <f t="array" aca="1" ref="A250" ca="1">GAMMALN({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B250">
@@ -8296,125 +8296,125 @@
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A251" cm="1">
-        <f t="array" ref="A251">GCD(D!B1:B2,2)</f>
+      <c r="A251" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A251" ca="1">_xlfn.GAMMALN.PRECISE(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B251">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C251">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D251" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E251" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A252" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A252" ca="1">_xlfn.GAMMALN.PRECISE({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B252">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C252">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D252" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E252" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A253" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A253" ca="1">_xlfn.GAUSS(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B253">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C253">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D253" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E253" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A254" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A254" ca="1">_xlfn.GAUSS({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B254">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C254">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D254" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E254" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A255" cm="1">
+        <f t="array" ref="A255">GCD(D!B1:B2,2)</f>
         <v>2</v>
       </c>
-      <c r="B251">
+      <c r="B255">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="C251">
+      <c r="C255">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="D251" t="str">
+      <c r="D255" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="E251" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A252" cm="1">
-        <f t="array" ref="A252">GCD({1;2},2)</f>
+      <c r="E255" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A256" cm="1">
+        <f t="array" ref="A256">GCD({1;2},2)</f>
         <v>1</v>
       </c>
-      <c r="B252">
+      <c r="B256">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="C252">
+      <c r="C256">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D252" t="str">
+      <c r="D256" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="E252" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A253" cm="1">
-        <f t="array" ref="A253">GCD(5,D!B1:B2)</f>
-        <v>1</v>
-      </c>
-      <c r="B253">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="C253">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="D253" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="E253" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A254" cm="1">
-        <f t="array" ref="A254">GCD(5,{1;2})</f>
-        <v>1</v>
-      </c>
-      <c r="B254">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="C254">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="D254" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="E254" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A255" t="e" cm="1">
-        <f t="array" ref="A255">GESTEP(D!B1:B2,4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B255">
-        <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="C255">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D255" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="E255" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A256" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A256" ca="1">GESTEP({1;2},4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B256">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C256">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D256" t="str">
-        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="E256" t="s">
@@ -8422,17 +8422,17 @@
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A257" t="e" cm="1">
-        <f t="array" ref="A257">GESTEP(5,D!B1:B2)</f>
-        <v>#VALUE!</v>
+      <c r="A257" cm="1">
+        <f t="array" ref="A257">GCD(5,D!B1:B2)</f>
+        <v>1</v>
       </c>
       <c r="B257">
         <f t="shared" ref="B257:B320" si="12">IF(ISERROR(A257),ERROR.TYPE(A257),IF(ISNUMBER(A257),0,IF(ISLOGICAL(A257),IF(A257,-1,-2),IF(ISTEXT(A257),-3,-4))))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C257">
         <f t="shared" ref="C257:C320" si="13">IF(ISNUMBER(A257),A257,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D257" t="str">
         <f t="shared" ref="D257:D320" si="14">IF(ISTEXT(A257),A257,"")</f>
@@ -8443,20 +8443,20 @@
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A258" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A258" ca="1">GESTEP(5,{1;2})</f>
-        <v>#VALUE!</v>
+      <c r="A258" cm="1">
+        <f t="array" ref="A258">GCD(5,{1;2})</f>
+        <v>1</v>
       </c>
       <c r="B258">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="C258">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="D258" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="E258" t="s">
@@ -8465,7 +8465,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" t="e" cm="1">
-        <f t="array" ref="A259">HEX2BIN(D!B1:B2,8)</f>
+        <f t="array" ref="A259">GESTEP(D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B259">
@@ -8486,7 +8486,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A260" ca="1">HEX2BIN({1;2},8)</f>
+        <f t="array" aca="1" ref="A260" ca="1">GESTEP({1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B260">
@@ -8507,7 +8507,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" t="e" cm="1">
-        <f t="array" ref="A261">HEX2BIN("F",D!B1:B2)</f>
+        <f t="array" ref="A261">GESTEP(5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B261">
@@ -8528,7 +8528,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A262" ca="1">HEX2BIN("F",{1;2})</f>
+        <f t="array" aca="1" ref="A262" ca="1">GESTEP(5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B262">
@@ -8549,7 +8549,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" t="e" cm="1">
-        <f t="array" ref="A263">HEX2DEC(D!B1:B2)</f>
+        <f t="array" ref="A263">HEX2BIN(D!B1:B2,8)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B263">
@@ -8570,7 +8570,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A264" ca="1">HEX2DEC({1;2})</f>
+        <f t="array" aca="1" ref="A264" ca="1">HEX2BIN({1;2},8)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B264">
@@ -8591,7 +8591,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" t="e" cm="1">
-        <f t="array" ref="A265">HEX2OCT(D!B1:B2,3)</f>
+        <f t="array" ref="A265">HEX2BIN("F",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B265">
@@ -8612,7 +8612,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A266" ca="1">HEX2OCT({1;2},3)</f>
+        <f t="array" aca="1" ref="A266" ca="1">HEX2BIN("F",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B266">
@@ -8633,7 +8633,7 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" t="e" cm="1">
-        <f t="array" ref="A267">HEX2OCT("F",D!B1:B2)</f>
+        <f t="array" ref="A267">HEX2DEC(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B267">
@@ -8654,7 +8654,7 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A268" ca="1">HEX2OCT("F",{1;2})</f>
+        <f t="array" aca="1" ref="A268" ca="1">HEX2DEC({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B268">
@@ -8674,20 +8674,20 @@
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A269" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A269" ca="1">HLOOKUP(D!B1:B2,D!L8:Q10,2,FALSE)</f>
+      <c r="A269" t="e" cm="1">
+        <f t="array" ref="A269">HEX2OCT(D!B1:B2,3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B269">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>3</v>
       </c>
       <c r="C269">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D269" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="E269" t="s">
@@ -8696,7 +8696,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A270" ca="1">HLOOKUP({1;2},D!L8:Q10,2,FALSE)</f>
+        <f t="array" aca="1" ref="A270" ca="1">HEX2OCT({1;2},3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B270">
@@ -8717,12 +8717,12 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" t="e" cm="1">
-        <f t="array" ref="A271">HLOOKUP(5,D!L8:Q10,D!B1:B2,FALSE)</f>
-        <v>#REF!</v>
+        <f t="array" ref="A271">HEX2OCT("F",D!B1:B2)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B271">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C271">
         <f t="shared" si="13"/>
@@ -8738,7 +8738,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A272" ca="1">HLOOKUP(5,D!L8:Q10,{1;2},FALSE)</f>
+        <f t="array" aca="1" ref="A272" ca="1">HEX2OCT("F",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B272">
@@ -8759,7 +8759,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A273" ca="1">HLOOKUP(5,D!L8:Q10,2,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A273" ca="1">HLOOKUP(D!B1:B2,D!L8:Q10,2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B273">
@@ -8780,7 +8780,7 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A274" ca="1">HLOOKUP(5,D!L8:Q10,2,{1;2})</f>
+        <f t="array" aca="1" ref="A274" ca="1">HLOOKUP({1;2},D!L8:Q10,2,FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B274">
@@ -8800,20 +8800,20 @@
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A275" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A275" ca="1">HOUR(D!B1:B2)</f>
-        <v>#VALUE!</v>
+      <c r="A275" t="e" cm="1">
+        <f t="array" ref="A275">HLOOKUP(5,D!L8:Q10,D!B1:B2,FALSE)</f>
+        <v>#REF!</v>
       </c>
       <c r="B275">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>4</v>
       </c>
       <c r="C275">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D275" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="E275" t="s">
@@ -8822,7 +8822,7 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A276" ca="1">HOUR({1;2})</f>
+        <f t="array" aca="1" ref="A276" ca="1">HLOOKUP(5,D!L8:Q10,{1;2},FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B276">
@@ -8843,7 +8843,7 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A277" ca="1">HYPERLINK(D!B1:B2,"x")</f>
+        <f t="array" aca="1" ref="A277" ca="1">HLOOKUP(5,D!L8:Q10,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B277">
@@ -8864,7 +8864,7 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A278" ca="1">HYPERLINK({1;2},"x")</f>
+        <f t="array" aca="1" ref="A278" ca="1">HLOOKUP(5,D!L8:Q10,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B278">
@@ -8885,7 +8885,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A279" ca="1">HYPERLINK("http://example.com",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A279" ca="1">HOUR(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B279">
@@ -8906,7 +8906,7 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A280" ca="1">HYPERLINK("http://example.com",{1;2})</f>
+        <f t="array" aca="1" ref="A280" ca="1">HOUR({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B280">
@@ -8927,7 +8927,7 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A281" ca="1">_xlfn.HYPGEOM.DIST(D!B1:B2,4,8,20,TRUE)</f>
+        <f t="array" aca="1" ref="A281" ca="1">HYPERLINK(D!B1:B2,"x")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B281">
@@ -8948,7 +8948,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A282" ca="1">_xlfn.HYPGEOM.DIST({1;2},4,8,20,TRUE)</f>
+        <f t="array" aca="1" ref="A282" ca="1">HYPERLINK({1;2},"x")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B282">
@@ -8969,7 +8969,7 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A283" ca="1">_xlfn.HYPGEOM.DIST(1,D!B1:B2,8,20,TRUE)</f>
+        <f t="array" aca="1" ref="A283" ca="1">HYPERLINK("http://example.com",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B283">
@@ -8990,7 +8990,7 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A284" ca="1">_xlfn.HYPGEOM.DIST(1,{1;2},8,20,TRUE)</f>
+        <f t="array" aca="1" ref="A284" ca="1">HYPERLINK("http://example.com",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B284">
@@ -9011,7 +9011,7 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A285" ca="1">_xlfn.HYPGEOM.DIST(1,4,D!B1:B2,20,TRUE)</f>
+        <f t="array" aca="1" ref="A285" ca="1">_xlfn.HYPGEOM.DIST(D!B1:B2,4,8,20,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B285">
@@ -9032,7 +9032,7 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A286" ca="1">_xlfn.HYPGEOM.DIST(1,4,{1;2},20,TRUE)</f>
+        <f t="array" aca="1" ref="A286" ca="1">_xlfn.HYPGEOM.DIST({1;2},4,8,20,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B286">
@@ -9053,7 +9053,7 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A287" ca="1">_xlfn.HYPGEOM.DIST(1,4,8,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A287" ca="1">_xlfn.HYPGEOM.DIST(1,D!B1:B2,8,20,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B287">
@@ -9074,7 +9074,7 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A288" ca="1">_xlfn.HYPGEOM.DIST(1,4,8,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A288" ca="1">_xlfn.HYPGEOM.DIST(1,{1;2},8,20,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B288">
@@ -9095,7 +9095,7 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A289" ca="1">_xlfn.HYPGEOM.DIST(1,4,8,20,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A289" ca="1">_xlfn.HYPGEOM.DIST(1,4,D!B1:B2,20,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B289">
@@ -9116,7 +9116,7 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A290" ca="1">_xlfn.HYPGEOM.DIST(1,4,8,20,{1;2})</f>
+        <f t="array" aca="1" ref="A290" ca="1">_xlfn.HYPGEOM.DIST(1,4,{1;2},20,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B290">
@@ -9137,7 +9137,7 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A291" ca="1">HYPGEOMDIST(D!B1:B2,4,8,20)</f>
+        <f t="array" aca="1" ref="A291" ca="1">_xlfn.HYPGEOM.DIST(1,4,8,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B291">
@@ -9158,7 +9158,7 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A292" ca="1">HYPGEOMDIST({1;2},4,8,20)</f>
+        <f t="array" aca="1" ref="A292" ca="1">_xlfn.HYPGEOM.DIST(1,4,8,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B292">
@@ -9179,7 +9179,7 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A293" ca="1">HYPGEOMDIST(1,D!B1:B2,8,20)</f>
+        <f t="array" aca="1" ref="A293" ca="1">_xlfn.HYPGEOM.DIST(1,4,8,20,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B293">
@@ -9200,7 +9200,7 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A294" ca="1">HYPGEOMDIST(1,{1;2},8,20)</f>
+        <f t="array" aca="1" ref="A294" ca="1">_xlfn.HYPGEOM.DIST(1,4,8,20,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B294">
@@ -9221,7 +9221,7 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A295" ca="1">HYPGEOMDIST(1,4,D!B1:B2,20)</f>
+        <f t="array" aca="1" ref="A295" ca="1">HYPGEOMDIST(D!B1:B2,4,8,20)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B295">
@@ -9242,7 +9242,7 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A296" ca="1">HYPGEOMDIST(1,4,{1;2},20)</f>
+        <f t="array" aca="1" ref="A296" ca="1">HYPGEOMDIST({1;2},4,8,20)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B296">
@@ -9263,7 +9263,7 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A297" ca="1">HYPGEOMDIST(1,4,8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A297" ca="1">HYPGEOMDIST(1,D!B1:B2,8,20)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B297">
@@ -9284,7 +9284,7 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A298" ca="1">HYPGEOMDIST(1,4,8,{1;2})</f>
+        <f t="array" aca="1" ref="A298" ca="1">HYPGEOMDIST(1,{1;2},8,20)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B298">
@@ -9305,7 +9305,7 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A299" ca="1">IF(D!B1:B2,"yes","no")</f>
+        <f t="array" aca="1" ref="A299" ca="1">HYPGEOMDIST(1,4,D!B1:B2,20)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B299">
@@ -9326,7 +9326,7 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A300" ca="1">IF({1;2},"yes","no")</f>
+        <f t="array" aca="1" ref="A300" ca="1">HYPGEOMDIST(1,4,{1;2},20)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B300">
@@ -9347,7 +9347,7 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A301" ca="1">IF(TRUE,D!B1:B2,"no")</f>
+        <f t="array" aca="1" ref="A301" ca="1">HYPGEOMDIST(1,4,8,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B301">
@@ -9368,7 +9368,7 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A302" ca="1">IF(TRUE,{1;2},"no")</f>
+        <f t="array" aca="1" ref="A302" ca="1">HYPGEOMDIST(1,4,8,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B302">
@@ -9388,134 +9388,134 @@
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A303" t="str" cm="1">
-        <f t="array" ref="A303">IF(TRUE,"yes",D!B1:B2)</f>
+      <c r="A303" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A303" ca="1">IF(D!B1:B2,"yes","no")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B303">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C303">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D303" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E303" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A304" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A304" ca="1">IF({1;2},"yes","no")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B304">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C304">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D304" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E304" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A305" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A305" ca="1">IF(TRUE,D!B1:B2,"no")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B305">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C305">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D305" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E305" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A306" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A306" ca="1">IF(TRUE,{1;2},"no")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B306">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C306">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D306" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E306" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A307" t="str" cm="1">
+        <f t="array" ref="A307">IF(TRUE,"yes",D!B1:B2)</f>
         <v>yes</v>
       </c>
-      <c r="B303">
+      <c r="B307">
         <f t="shared" si="12"/>
         <v>-3</v>
       </c>
-      <c r="C303">
+      <c r="C307">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="D303" t="str">
+      <c r="D307" t="str">
         <f t="shared" si="14"/>
         <v>yes</v>
       </c>
-      <c r="E303" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A304" t="str" cm="1">
-        <f t="array" ref="A304">IF(TRUE,"yes",{1;2})</f>
+      <c r="E307" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A308" t="str" cm="1">
+        <f t="array" ref="A308">IF(TRUE,"yes",{1;2})</f>
         <v>yes</v>
       </c>
-      <c r="B304">
+      <c r="B308">
         <f t="shared" si="12"/>
         <v>-3</v>
       </c>
-      <c r="C304">
+      <c r="C308">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="D304" t="str">
+      <c r="D308" t="str">
         <f t="shared" si="14"/>
         <v>yes</v>
       </c>
-      <c r="E304" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A305" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A305" ca="1">IFERROR(D!B1:B2,"err")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B305">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C305">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D305" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-      <c r="E305" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A306" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A306" ca="1">IFERROR({1;2},"err")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B306">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C306">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D306" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-      <c r="E306" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A307" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A307" ca="1">IFERROR(D!A7,D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B307">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C307">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D307" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-      <c r="E307" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A308" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A308" ca="1">IFERROR(D!A7,{1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B308">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C308">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D308" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
       <c r="E308" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A309" ca="1">_xlfn.IFNA(D!B1:B2,"nf")</f>
+        <f t="array" aca="1" ref="A309" ca="1">IFERROR(D!B1:B2,"err")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B309">
@@ -9536,7 +9536,7 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A310" ca="1">_xlfn.IFNA({1;2},"nf")</f>
+        <f t="array" aca="1" ref="A310" ca="1">IFERROR({1;2},"err")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B310">
@@ -9557,7 +9557,7 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A311" ca="1">_xlfn.IFNA(D!A8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A311" ca="1">IFERROR(D!A7,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B311">
@@ -9578,7 +9578,7 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A312" ca="1">_xlfn.IFNA(D!A8,{1;2})</f>
+        <f t="array" aca="1" ref="A312" ca="1">IFERROR(D!A7,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B312">
@@ -9599,7 +9599,7 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A313" ca="1">_xlfn.IFS(D!B1:B2,1,TRUE,2)</f>
+        <f t="array" aca="1" ref="A313" ca="1">_xlfn.IFNA(D!B1:B2,"nf")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B313">
@@ -9620,7 +9620,7 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A314" ca="1">_xlfn.IFS({1;2},1,TRUE,2)</f>
+        <f t="array" aca="1" ref="A314" ca="1">_xlfn.IFNA({1;2},"nf")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B314">
@@ -9640,125 +9640,125 @@
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A315" cm="1">
-        <f t="array" ref="A315">_xlfn.IFS(FALSE,D!B1:B2,TRUE,2)</f>
+      <c r="A315" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A315" ca="1">_xlfn.IFNA(D!A8,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B315">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C315">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D315" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E315" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A316" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A316" ca="1">_xlfn.IFNA(D!A8,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B316">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C316">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D316" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E316" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A317" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A317" ca="1">_xlfn.IFS(D!B1:B2,1,TRUE,2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B317">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C317">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D317" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E317" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A318" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A318" ca="1">_xlfn.IFS({1;2},1,TRUE,2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B318">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C318">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D318" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E318" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A319" cm="1">
+        <f t="array" ref="A319">_xlfn.IFS(FALSE,D!B1:B2,TRUE,2)</f>
         <v>2</v>
       </c>
-      <c r="B315">
+      <c r="B319">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="C315">
+      <c r="C319">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="D315" t="str">
+      <c r="D319" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="E315" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A316" cm="1">
-        <f t="array" ref="A316">_xlfn.IFS(FALSE,{1;2},TRUE,2)</f>
+      <c r="E319" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A320" cm="1">
+        <f t="array" ref="A320">_xlfn.IFS(FALSE,{1;2},TRUE,2)</f>
         <v>2</v>
       </c>
-      <c r="B316">
+      <c r="B320">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="C316">
+      <c r="C320">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="D316" t="str">
+      <c r="D320" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="E316" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A317" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A317" ca="1">_xlfn.IFS(FALSE,1,D!B1:B2,2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B317">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C317">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D317" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-      <c r="E317" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A318" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A318" ca="1">_xlfn.IFS(FALSE,1,{1;2},2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B318">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C318">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D318" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-      <c r="E318" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A319" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A319" ca="1">_xlfn.IFS(FALSE,1,TRUE,D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B319">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C319">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D319" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-      <c r="E319" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A320" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A320" ca="1">_xlfn.IFS(FALSE,1,TRUE,{1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B320">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C320">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D320" t="str">
-        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="E320" t="s">
@@ -9766,20 +9766,20 @@
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A321" t="e" cm="1">
-        <f t="array" ref="A321">IMABS(D!B1:B2)</f>
+      <c r="A321" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A321" ca="1">_xlfn.IFS(FALSE,1,D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B321">
-        <f t="shared" ref="B321:B384" si="15">IF(ISERROR(A321),ERROR.TYPE(A321),IF(ISNUMBER(A321),0,IF(ISLOGICAL(A321),IF(A321,-1,-2),IF(ISTEXT(A321),-3,-4))))</f>
-        <v>3</v>
+        <f t="shared" ref="B321:B384" ca="1" si="15">IF(ISERROR(A321),ERROR.TYPE(A321),IF(ISNUMBER(A321),0,IF(ISLOGICAL(A321),IF(A321,-1,-2),IF(ISTEXT(A321),-3,-4))))</f>
+        <v>9</v>
       </c>
       <c r="C321">
-        <f t="shared" ref="C321:C384" si="16">IF(ISNUMBER(A321),A321,0)</f>
+        <f t="shared" ref="C321:C384" ca="1" si="16">IF(ISNUMBER(A321),A321,0)</f>
         <v>0</v>
       </c>
       <c r="D321" t="str">
-        <f t="shared" ref="D321:D384" si="17">IF(ISTEXT(A321),A321,"")</f>
+        <f t="shared" ref="D321:D384" ca="1" si="17">IF(ISTEXT(A321),A321,"")</f>
         <v/>
       </c>
       <c r="E321" t="s">
@@ -9788,7 +9788,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A322" ca="1">IMABS({1;2})</f>
+        <f t="array" aca="1" ref="A322" ca="1">_xlfn.IFS(FALSE,1,{1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B322">
@@ -9808,20 +9808,20 @@
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A323" t="e" cm="1">
-        <f t="array" ref="A323">IMAGINARY(D!B1:B2)</f>
+      <c r="A323" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A323" ca="1">_xlfn.IFS(FALSE,1,TRUE,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B323">
-        <f t="shared" si="15"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
       </c>
       <c r="C323">
-        <f t="shared" si="16"/>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
       <c r="D323" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="E323" t="s">
@@ -9830,7 +9830,7 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A324" ca="1">IMAGINARY({1;2})</f>
+        <f t="array" aca="1" ref="A324" ca="1">_xlfn.IFS(FALSE,1,TRUE,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B324">
@@ -9851,7 +9851,7 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325" t="e" cm="1">
-        <f t="array" ref="A325">IMARGUMENT(D!B1:B2)</f>
+        <f t="array" ref="A325">IMABS(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B325">
@@ -9872,7 +9872,7 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A326" ca="1">IMARGUMENT({1;2})</f>
+        <f t="array" aca="1" ref="A326" ca="1">IMABS({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B326">
@@ -9893,7 +9893,7 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A327" t="e" cm="1">
-        <f t="array" ref="A327">IMCONJUGATE(D!B1:B2)</f>
+        <f t="array" ref="A327">IMAGINARY(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B327">
@@ -9914,7 +9914,7 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A328" ca="1">IMCONJUGATE({1;2})</f>
+        <f t="array" aca="1" ref="A328" ca="1">IMAGINARY({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B328">
@@ -9935,7 +9935,7 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" t="e" cm="1">
-        <f t="array" ref="A329">IMCOS(D!B1:B2)</f>
+        <f t="array" ref="A329">IMARGUMENT(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B329">
@@ -9956,7 +9956,7 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A330" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A330" ca="1">IMCOS({1;2})</f>
+        <f t="array" aca="1" ref="A330" ca="1">IMARGUMENT({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B330">
@@ -9977,7 +9977,7 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A331" t="e" cm="1">
-        <f t="array" ref="A331">_xlfn.IMCOSH(D!B1:B2)</f>
+        <f t="array" ref="A331">IMCONJUGATE(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B331">
@@ -9998,7 +9998,7 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A332" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A332" ca="1">_xlfn.IMCOSH({1;2})</f>
+        <f t="array" aca="1" ref="A332" ca="1">IMCONJUGATE({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B332">
@@ -10019,7 +10019,7 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333" t="e" cm="1">
-        <f t="array" ref="A333">_xlfn.IMCOT(D!B1:B2)</f>
+        <f t="array" ref="A333">IMCOS(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B333">
@@ -10040,7 +10040,7 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A334" ca="1">_xlfn.IMCOT({1;2})</f>
+        <f t="array" aca="1" ref="A334" ca="1">IMCOS({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B334">
@@ -10061,7 +10061,7 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" t="e" cm="1">
-        <f t="array" ref="A335">_xlfn.IMCSC(D!B1:B2)</f>
+        <f t="array" ref="A335">_xlfn.IMCOSH(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B335">
@@ -10082,7 +10082,7 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A336" ca="1">_xlfn.IMCSC({1;2})</f>
+        <f t="array" aca="1" ref="A336" ca="1">_xlfn.IMCOSH({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B336">
@@ -10103,7 +10103,7 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" t="e" cm="1">
-        <f t="array" ref="A337">_xlfn.IMCSCH(D!B1:B2)</f>
+        <f t="array" ref="A337">_xlfn.IMCOT(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B337">
@@ -10124,7 +10124,7 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A338" ca="1">_xlfn.IMCSCH({1;2})</f>
+        <f t="array" aca="1" ref="A338" ca="1">_xlfn.IMCOT({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B338">
@@ -10145,7 +10145,7 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" t="e" cm="1">
-        <f t="array" ref="A339">IMDIV(D!B1:B2,"10+24i")</f>
+        <f t="array" ref="A339">_xlfn.IMCSC(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B339">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A340" ca="1">IMDIV({1;2},"10+24i")</f>
+        <f t="array" aca="1" ref="A340" ca="1">_xlfn.IMCSC({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B340">
@@ -10187,7 +10187,7 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A341" t="e" cm="1">
-        <f t="array" ref="A341">IMDIV("-238+240i",D!B1:B2)</f>
+        <f t="array" ref="A341">_xlfn.IMCSCH(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B341">
@@ -10208,7 +10208,7 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A342" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A342" ca="1">IMDIV("-238+240i",{1;2})</f>
+        <f t="array" aca="1" ref="A342" ca="1">_xlfn.IMCSCH({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B342">
@@ -10229,7 +10229,7 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343" t="e" cm="1">
-        <f t="array" ref="A343">IMEXP(D!B1:B2)</f>
+        <f t="array" ref="A343">IMDIV(D!B1:B2,"10+24i")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B343">
@@ -10250,7 +10250,7 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A344" ca="1">IMEXP({1;2})</f>
+        <f t="array" aca="1" ref="A344" ca="1">IMDIV({1;2},"10+24i")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B344">
@@ -10271,7 +10271,7 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345" t="e" cm="1">
-        <f t="array" ref="A345">IMLN(D!B1:B2)</f>
+        <f t="array" ref="A345">IMDIV("-238+240i",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B345">
@@ -10292,7 +10292,7 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A346" ca="1">IMLN({1;2})</f>
+        <f t="array" aca="1" ref="A346" ca="1">IMDIV("-238+240i",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B346">
@@ -10313,7 +10313,7 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347" t="e" cm="1">
-        <f t="array" ref="A347">IMLOG10(D!B1:B2)</f>
+        <f t="array" ref="A347">IMEXP(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B347">
@@ -10334,7 +10334,7 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A348" ca="1">IMLOG10({1;2})</f>
+        <f t="array" aca="1" ref="A348" ca="1">IMEXP({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B348">
@@ -10355,7 +10355,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" t="e" cm="1">
-        <f t="array" ref="A349">IMLOG2(D!B1:B2)</f>
+        <f t="array" ref="A349">IMLN(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B349">
@@ -10376,7 +10376,7 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A350" ca="1">IMLOG2({1;2})</f>
+        <f t="array" aca="1" ref="A350" ca="1">IMLN({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B350">
@@ -10397,7 +10397,7 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" t="e" cm="1">
-        <f t="array" ref="A351">IMPOWER(D!B1:B2,3)</f>
+        <f t="array" ref="A351">IMLOG10(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B351">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A352" ca="1">IMPOWER({1;2},3)</f>
+        <f t="array" aca="1" ref="A352" ca="1">IMLOG10({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B352">
@@ -10439,7 +10439,7 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" t="e" cm="1">
-        <f t="array" ref="A353">IMPOWER("2+3i",D!B1:B2)</f>
+        <f t="array" ref="A353">IMLOG2(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B353">
@@ -10460,7 +10460,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A354" ca="1">IMPOWER("2+3i",{1;2})</f>
+        <f t="array" aca="1" ref="A354" ca="1">IMLOG2({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B354">
@@ -10480,13 +10480,13 @@
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A355" t="str" cm="1">
-        <f t="array" ref="A355">IMPRODUCT(D!B1:B2,"5-3i")</f>
-        <v>160-96i</v>
+      <c r="A355" t="e" cm="1">
+        <f t="array" ref="A355">IMPOWER(D!B1:B2,3)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B355">
         <f t="shared" si="15"/>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="C355">
         <f t="shared" si="16"/>
@@ -10494,162 +10494,162 @@
       </c>
       <c r="D355" t="str">
         <f t="shared" si="17"/>
-        <v>160-96i</v>
+        <v/>
       </c>
       <c r="E355" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A356" t="str" cm="1">
-        <f t="array" ref="A356">IMPRODUCT({1;2},"5-3i")</f>
-        <v>10-6i</v>
+      <c r="A356" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A356" ca="1">IMPOWER({1;2},3)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B356">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C356">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D356" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E356" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A357" t="e" cm="1">
+        <f t="array" ref="A357">IMPOWER("2+3i",D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B357">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="C357">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D357" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="E357" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A358" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A358" ca="1">IMPOWER("2+3i",{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B358">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C358">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D358" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E358" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A359" t="str" cm="1">
+        <f t="array" ref="A359">IMPRODUCT(D!B1:B2,"5-3i")</f>
+        <v>160-96i</v>
+      </c>
+      <c r="B359">
         <f t="shared" si="15"/>
         <v>-3</v>
       </c>
-      <c r="C356">
+      <c r="C359">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D356" t="str">
+      <c r="D359" t="str">
+        <f t="shared" si="17"/>
+        <v>160-96i</v>
+      </c>
+      <c r="E359" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A360" t="str" cm="1">
+        <f t="array" ref="A360">IMPRODUCT({1;2},"5-3i")</f>
+        <v>10-6i</v>
+      </c>
+      <c r="B360">
+        <f t="shared" si="15"/>
+        <v>-3</v>
+      </c>
+      <c r="C360">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D360" t="str">
         <f t="shared" si="17"/>
         <v>10-6i</v>
       </c>
-      <c r="E356" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A357" t="str" cm="1">
-        <f t="array" ref="A357">IMPRODUCT("3+4i",D!B1:B2)</f>
+      <c r="E360" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A361" t="str" cm="1">
+        <f t="array" ref="A361">IMPRODUCT("3+4i",D!B1:B2)</f>
         <v>96+128i</v>
       </c>
-      <c r="B357">
+      <c r="B361">
         <f t="shared" si="15"/>
         <v>-3</v>
       </c>
-      <c r="C357">
+      <c r="C361">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D357" t="str">
+      <c r="D361" t="str">
         <f t="shared" si="17"/>
         <v>96+128i</v>
       </c>
-      <c r="E357" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A358" t="str" cm="1">
-        <f t="array" ref="A358">IMPRODUCT("3+4i",{1;2})</f>
+      <c r="E361" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A362" t="str" cm="1">
+        <f t="array" ref="A362">IMPRODUCT("3+4i",{1;2})</f>
         <v>6+8i</v>
       </c>
-      <c r="B358">
+      <c r="B362">
         <f t="shared" si="15"/>
         <v>-3</v>
       </c>
-      <c r="C358">
+      <c r="C362">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D358" t="str">
+      <c r="D362" t="str">
         <f t="shared" si="17"/>
         <v>6+8i</v>
       </c>
-      <c r="E358" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A359" t="e" cm="1">
-        <f t="array" ref="A359">IMREAL(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B359">
-        <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-      <c r="C359">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D359" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E359" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A360" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A360" ca="1">IMREAL({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B360">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C360">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D360" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E360" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A361" t="e" cm="1">
-        <f t="array" ref="A361">_xlfn.IMSEC(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B361">
-        <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-      <c r="C361">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D361" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E361" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A362" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A362" ca="1">_xlfn.IMSEC({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B362">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C362">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D362" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
       <c r="E362" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363" t="e" cm="1">
-        <f t="array" ref="A363">_xlfn.IMSECH(D!B1:B2)</f>
+        <f t="array" ref="A363">IMREAL(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B363">
@@ -10670,7 +10670,7 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A364" ca="1">_xlfn.IMSECH({1;2})</f>
+        <f t="array" aca="1" ref="A364" ca="1">IMREAL({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B364">
@@ -10691,7 +10691,7 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365" t="e" cm="1">
-        <f t="array" ref="A365">IMSIN(D!B1:B2)</f>
+        <f t="array" ref="A365">_xlfn.IMSEC(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B365">
@@ -10712,7 +10712,7 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A366" ca="1">IMSIN({1;2})</f>
+        <f t="array" aca="1" ref="A366" ca="1">_xlfn.IMSEC({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B366">
@@ -10733,7 +10733,7 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367" t="e" cm="1">
-        <f t="array" ref="A367">_xlfn.IMSINH(D!B1:B2)</f>
+        <f t="array" ref="A367">_xlfn.IMSECH(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B367">
@@ -10754,7 +10754,7 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A368" ca="1">_xlfn.IMSINH({1;2})</f>
+        <f t="array" aca="1" ref="A368" ca="1">_xlfn.IMSECH({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B368">
@@ -10775,7 +10775,7 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A369" t="e" cm="1">
-        <f t="array" ref="A369">IMSQRT(D!B1:B2)</f>
+        <f t="array" ref="A369">IMSIN(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B369">
@@ -10796,7 +10796,7 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A370" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A370" ca="1">IMSQRT({1;2})</f>
+        <f t="array" aca="1" ref="A370" ca="1">IMSIN({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B370">
@@ -10817,7 +10817,7 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A371" t="e" cm="1">
-        <f t="array" ref="A371">IMSUB(D!B1:B2,"5+3i")</f>
+        <f t="array" ref="A371">_xlfn.IMSINH(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B371">
@@ -10838,7 +10838,7 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A372" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A372" ca="1">IMSUB({1;2},"5+3i")</f>
+        <f t="array" aca="1" ref="A372" ca="1">_xlfn.IMSINH({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B372">
@@ -10859,7 +10859,7 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A373" t="e" cm="1">
-        <f t="array" ref="A373">IMSUB("13+4i",D!B1:B2)</f>
+        <f t="array" ref="A373">IMSQRT(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B373">
@@ -10880,7 +10880,7 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A374" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A374" ca="1">IMSUB("13+4i",{1;2})</f>
+        <f t="array" aca="1" ref="A374" ca="1">IMSQRT({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B374">
@@ -10900,13 +10900,13 @@
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A375" t="str" cm="1">
-        <f t="array" ref="A375">IMSUM(D!B1:B2,"5-3i")</f>
-        <v>17-3i</v>
+      <c r="A375" t="e" cm="1">
+        <f t="array" ref="A375">IMSUB(D!B1:B2,"5+3i")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B375">
         <f t="shared" si="15"/>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="C375">
         <f t="shared" si="16"/>
@@ -10914,174 +10914,174 @@
       </c>
       <c r="D375" t="str">
         <f t="shared" si="17"/>
-        <v>17-3i</v>
+        <v/>
       </c>
       <c r="E375" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A376" t="str" cm="1">
-        <f t="array" ref="A376">IMSUM({1;2},"5-3i")</f>
-        <v>8-3i</v>
+      <c r="A376" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A376" ca="1">IMSUB({1;2},"5+3i")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B376">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C376">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D376" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E376" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A377" t="e" cm="1">
+        <f t="array" ref="A377">IMSUB("13+4i",D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B377">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="C377">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D377" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="E377" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A378" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A378" ca="1">IMSUB("13+4i",{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B378">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C378">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D378" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E378" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A379" t="str" cm="1">
+        <f t="array" ref="A379">IMSUM(D!B1:B2,"5-3i")</f>
+        <v>17-3i</v>
+      </c>
+      <c r="B379">
         <f t="shared" si="15"/>
         <v>-3</v>
       </c>
-      <c r="C376">
+      <c r="C379">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D376" t="str">
+      <c r="D379" t="str">
+        <f t="shared" si="17"/>
+        <v>17-3i</v>
+      </c>
+      <c r="E379" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A380" t="str" cm="1">
+        <f t="array" ref="A380">IMSUM({1;2},"5-3i")</f>
+        <v>8-3i</v>
+      </c>
+      <c r="B380">
+        <f t="shared" si="15"/>
+        <v>-3</v>
+      </c>
+      <c r="C380">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D380" t="str">
         <f t="shared" si="17"/>
         <v>8-3i</v>
       </c>
-      <c r="E376" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A377" t="str" cm="1">
-        <f t="array" ref="A377">IMSUM("3+4i",D!B1:B2)</f>
+      <c r="E380" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A381" t="str" cm="1">
+        <f t="array" ref="A381">IMSUM("3+4i",D!B1:B2)</f>
         <v>15+4i</v>
       </c>
-      <c r="B377">
+      <c r="B381">
         <f t="shared" si="15"/>
         <v>-3</v>
       </c>
-      <c r="C377">
+      <c r="C381">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D377" t="str">
+      <c r="D381" t="str">
         <f t="shared" si="17"/>
         <v>15+4i</v>
       </c>
-      <c r="E377" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A378" t="str" cm="1">
-        <f t="array" ref="A378">IMSUM("3+4i",{1;2})</f>
+      <c r="E381" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A382" t="str" cm="1">
+        <f t="array" ref="A382">IMSUM("3+4i",{1;2})</f>
         <v>6+4i</v>
       </c>
-      <c r="B378">
+      <c r="B382">
         <f t="shared" si="15"/>
         <v>-3</v>
       </c>
-      <c r="C378">
+      <c r="C382">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D378" t="str">
+      <c r="D382" t="str">
         <f t="shared" si="17"/>
         <v>6+4i</v>
       </c>
-      <c r="E378" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A379" t="e" cm="1">
-        <f t="array" ref="A379">_xlfn.IMTAN(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B379">
+      <c r="E382" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A383" t="e" cm="1">
+        <f t="array" ref="A383">_xlfn.IMTAN(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B383">
         <f t="shared" si="15"/>
         <v>3</v>
       </c>
-      <c r="C379">
+      <c r="C383">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D379" t="str">
+      <c r="D383" t="str">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E379" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A380" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A380" ca="1">_xlfn.IMTAN({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B380">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C380">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D380" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E380" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A381" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A381" ca="1">INDEX(D!L1:N6,D!B1:B2,3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B381">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C381">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D381" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E381" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A382" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A382" ca="1">INDEX(D!L1:N6,{1;2},3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B382">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C382">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D382" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E382" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A383" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A383" ca="1">INDEX(D!L1:N6,2,D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B383">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C383">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D383" t="str">
-        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="E383" t="s">
@@ -11090,7 +11090,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A384" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A384" ca="1">INDEX(D!L1:N6,2,{1;2})</f>
+        <f t="array" aca="1" ref="A384" ca="1">_xlfn.IMTAN({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B384">
@@ -11111,7 +11111,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A385" ca="1">INT(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A385" ca="1">INDEX(D!L1:N6,D!B1:B2,3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B385">
@@ -11132,7 +11132,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A386" ca="1">INT({1;2})</f>
+        <f t="array" aca="1" ref="A386" ca="1">INDEX(D!L1:N6,{1;2},3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B386">
@@ -11152,20 +11152,20 @@
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A387" t="e" cm="1">
-        <f t="array" ref="A387">INTRATE(D!B1:B2,DATE(2008,5,15),1000000,1014420,2)</f>
+      <c r="A387" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A387" ca="1">INDEX(D!L1:N6,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B387">
-        <f t="shared" si="18"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>9</v>
       </c>
       <c r="C387">
-        <f t="shared" si="19"/>
+        <f t="shared" ca="1" si="19"/>
         <v>0</v>
       </c>
       <c r="D387" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="E387" t="s">
@@ -11174,7 +11174,7 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A388" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A388" ca="1">INTRATE({1;2},DATE(2008,5,15),1000000,1014420,2)</f>
+        <f t="array" aca="1" ref="A388" ca="1">INDEX(D!L1:N6,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B388">
@@ -11194,20 +11194,20 @@
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A389" t="e" cm="1">
-        <f t="array" ref="A389">INTRATE(DATE(2008,2,15),D!B1:B2,1000000,1014420,2)</f>
+      <c r="A389" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A389" ca="1">INT(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B389">
-        <f t="shared" si="18"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>9</v>
       </c>
       <c r="C389">
-        <f t="shared" si="19"/>
+        <f t="shared" ca="1" si="19"/>
         <v>0</v>
       </c>
       <c r="D389" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="E389" t="s">
@@ -11216,7 +11216,7 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A390" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A390" ca="1">INTRATE(DATE(2008,2,15),{1;2},1000000,1014420,2)</f>
+        <f t="array" aca="1" ref="A390" ca="1">INT({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B390">
@@ -11237,7 +11237,7 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A391" t="e" cm="1">
-        <f t="array" ref="A391">INTRATE(DATE(2008,2,15),DATE(2008,5,15),D!B1:B2,1014420,2)</f>
+        <f t="array" ref="A391">INTRATE(D!B1:B2,DATE(2008,5,15),1000000,1014420,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B391">
@@ -11258,7 +11258,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A392" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A392" ca="1">INTRATE(DATE(2008,2,15),DATE(2008,5,15),{1;2},1014420,2)</f>
+        <f t="array" aca="1" ref="A392" ca="1">INTRATE({1;2},DATE(2008,5,15),1000000,1014420,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B392">
@@ -11279,7 +11279,7 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A393" t="e" cm="1">
-        <f t="array" ref="A393">INTRATE(DATE(2008,2,15),DATE(2008,5,15),1000000,D!B1:B2,2)</f>
+        <f t="array" ref="A393">INTRATE(DATE(2008,2,15),D!B1:B2,1000000,1014420,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B393">
@@ -11300,7 +11300,7 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A394" ca="1">INTRATE(DATE(2008,2,15),DATE(2008,5,15),1000000,{1;2},2)</f>
+        <f t="array" aca="1" ref="A394" ca="1">INTRATE(DATE(2008,2,15),{1;2},1000000,1014420,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B394">
@@ -11321,7 +11321,7 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395" t="e" cm="1">
-        <f t="array" ref="A395">INTRATE(DATE(2008,2,15),DATE(2008,5,15),1000000,1014420,D!B1:B2)</f>
+        <f t="array" ref="A395">INTRATE(DATE(2008,2,15),DATE(2008,5,15),D!B1:B2,1014420,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B395">
@@ -11342,7 +11342,7 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A396" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A396" ca="1">INTRATE(DATE(2008,2,15),DATE(2008,5,15),1000000,1014420,{1;2})</f>
+        <f t="array" aca="1" ref="A396" ca="1">INTRATE(DATE(2008,2,15),DATE(2008,5,15),{1;2},1014420,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B396">
@@ -11362,20 +11362,20 @@
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A397" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A397" ca="1">IPMT(D!B1:B2,1,36,8000)</f>
+      <c r="A397" t="e" cm="1">
+        <f t="array" ref="A397">INTRATE(DATE(2008,2,15),DATE(2008,5,15),1000000,D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B397">
-        <f t="shared" ca="1" si="18"/>
-        <v>9</v>
+        <f t="shared" si="18"/>
+        <v>3</v>
       </c>
       <c r="C397">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="D397" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="E397" t="s">
@@ -11384,7 +11384,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A398" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A398" ca="1">IPMT({1;2},1,36,8000)</f>
+        <f t="array" aca="1" ref="A398" ca="1">INTRATE(DATE(2008,2,15),DATE(2008,5,15),1000000,{1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B398">
@@ -11404,20 +11404,20 @@
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A399" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A399" ca="1">IPMT(0.00833333333333333,D!B1:B2,36,8000)</f>
+      <c r="A399" t="e" cm="1">
+        <f t="array" ref="A399">INTRATE(DATE(2008,2,15),DATE(2008,5,15),1000000,1014420,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B399">
-        <f t="shared" ca="1" si="18"/>
-        <v>9</v>
+        <f t="shared" si="18"/>
+        <v>3</v>
       </c>
       <c r="C399">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="D399" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="E399" t="s">
@@ -11426,7 +11426,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A400" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A400" ca="1">IPMT(0.00833333333333333,{1;2},36,8000)</f>
+        <f t="array" aca="1" ref="A400" ca="1">INTRATE(DATE(2008,2,15),DATE(2008,5,15),1000000,1014420,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B400">
